--- a/results/Int Task Remove ACC -0.8/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7025408818923782</v>
+        <v>0.7130075678808949</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7001638722675645</v>
+        <v>0.71770794789291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6998854758310389</v>
+        <v>0.7168029396412607</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7005333674748546</v>
+        <v>0.7159302907985317</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7023161246934649</v>
+        <v>0.7108816954079185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7039490437794664</v>
+        <v>0.716176327826137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6846536910126666</v>
+        <v>0.7145059492069834</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6830420517553573</v>
+        <v>0.7162887064255938</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6830420517553573</v>
+        <v>0.7042691205416121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6812056552991346</v>
+        <v>0.6956439311335501</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6807399611968479</v>
+        <v>0.6956439311335501</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6825814577773026</v>
+        <v>0.6976463454268418</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6758939638446917</v>
+        <v>0.6946052644537521</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.677837638776139</v>
+        <v>0.7043542398563805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6570702846361747</v>
+        <v>0.7081232316638223</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6570702846361747</v>
+        <v>0.6898333068361362</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6562938346884422</v>
+        <v>0.6849132697494397</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6528670788036023</v>
+        <v>0.6791418636487063</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6406440155493994</v>
+        <v>0.6783603135767418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6434118002101954</v>
+        <v>0.6632256069851301</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6389106767759336</v>
+        <v>0.6529836781955268</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6375552747946935</v>
+        <v>0.664751247595907</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6380371486014405</v>
+        <v>0.6652382215268857</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.636399129391207</v>
+        <v>0.6652382215268857</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6303535476464158</v>
+        <v>0.6652382215268857</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.625245333562194</v>
+        <v>0.6681405439475947</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.625245333562194</v>
+        <v>0.6547289758809849</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6259357848633941</v>
+        <v>0.6544880389776115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6259357848633941</v>
+        <v>0.652309406598787</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6253789919903429</v>
+        <v>0.6503069923054954</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6147522676207533</v>
+        <v>0.6318902678374207</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6181892237540572</v>
+        <v>0.6415166643921285</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6109236571197031</v>
+        <v>0.6186318793641236</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6074714006137032</v>
+        <v>0.6080213346989942</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6198059631355985</v>
+        <v>0.6107091001692537</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6164055872036828</v>
+        <v>0.6083746502018242</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6227712457106196</v>
+        <v>0.5521633671793992</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6145428107945361</v>
+        <v>0.5671260764779457</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6040258270291108</v>
+        <v>0.5714713823236025</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6025214662470261</v>
+        <v>0.5947110656516129</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6083677914140639</v>
+        <v>0.600916685777477</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.59904705058057</v>
+        <v>0.6017935554126739</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6001666157826686</v>
+        <v>0.6019433935452828</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.595064381154443</v>
+        <v>0.5972744936104237</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5820921272371959</v>
+        <v>0.579023786979418</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5868563467352873</v>
+        <v>0.5826804001874032</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5894368337303223</v>
+        <v>0.5900361862607577</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.554815255913682</v>
+        <v>0.5879426731967016</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5660787923468591</v>
+        <v>0.5859393795716459</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5683808829053685</v>
+        <v>0.6027504442384073</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5678240900323173</v>
+        <v>0.6069102110818313</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5716841806105235</v>
+        <v>0.6066318146453057</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5654956195208838</v>
+        <v>0.583001356281313</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5559510008202406</v>
+        <v>0.5788892492195051</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.555672604383715</v>
+        <v>0.5805596278386588</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5359115575146285</v>
+        <v>0.5879103137877814</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.552593184545709</v>
+        <v>0.588708043564206</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5379786906257606</v>
+        <v>0.5585408087319754</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5379786906257606</v>
+        <v>0.5585408087319754</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5314308345772947</v>
+        <v>0.5566184136292203</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5330152145499159</v>
+        <v>0.567111479570661</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4914882443895116</v>
+        <v>0.5318879112282928</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4911187491822214</v>
+        <v>0.5381411911357731</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.487284159225175</v>
+        <v>0.5375843982627219</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4864966296972144</v>
+        <v>0.539870309116771</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4875727559101646</v>
+        <v>0.5228021278421762</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4326692150873633</v>
+        <v>0.5212977670600915</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4331885484272624</v>
+        <v>0.5188620180734334</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4616521658996549</v>
+        <v>0.5156072594816585</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4574839574712951</v>
+        <v>0.5147882498765418</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4734494567136629</v>
+        <v>0.5238629536824304</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4766343963633652</v>
+        <v>0.5238629536824304</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4766343963633652</v>
+        <v>0.5261812239453998</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4828867969390813</v>
+        <v>0.5258977273846422</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4738129724649569</v>
+        <v>0.5173951168245008</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4775657845679385</v>
+        <v>0.5005193333398991</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4600396473105814</v>
+        <v>0.5005193333398991</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4652321013778073</v>
+        <v>0.5005193333398991</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4613447515149128</v>
+        <v>0.5005193333398991</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4808316227399415</v>
+        <v>0.5005193333398991</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4831822524118312</v>
+        <v>0.5016329190860015</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4962004074471662</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4998893800640716</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4896483306062324</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4865799903484546</v>
+        <v>0.5008351893095768</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4940958148028819</v>
+        <v>0.5008351893095768</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5026401056886434</v>
+        <v>0.5021522524259004</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5024528080228823</v>
+        <v>0.5002034773702212</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5024528080228823</v>
+        <v>0.4999625404668478</v>
       </c>
     </row>
   </sheetData>
